--- a/plantillas_excel/informes_rrhh/anexo_template.xlsx
+++ b/plantillas_excel/informes_rrhh/anexo_template.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo 14" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo 14A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo 17" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo 17.1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Modelo 14'!$7:$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Modelo 14A'!$7:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Modelo 17'!$7:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Modelo 17.1'!$7:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -552,7 +552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Anexo No 14</t>
+          <t>Anexo No 17</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Anexo No 14-A</t>
+          <t>Anexo No 17.1</t>
         </is>
       </c>
     </row>
